--- a/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
+++ b/docs/oc-mensuales/adquisicion-de-vehiculos-y-maquinaria/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M57"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34833204</v>
+        <v>37416.03</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>54683118</v>
+        <v>58737.79</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>16383300.01</v>
+        <v>17598.1</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>34821000.55</v>
+        <v>37402.92</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>708666</v>
+        <v>761.21</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>28548100</v>
+        <v>30664.9</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>20896289.33</v>
+        <v>22445.72</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>17140199.51</v>
+        <v>18411.12</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>32841000.01</v>
+        <v>35276.11</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1110519</v>
+        <v>1192.86</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>40514859</v>
+        <v>43518.97</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>48762737.1</v>
+        <v>52378.42</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>34425299.37</v>
+        <v>36977.88</v>
       </c>
     </row>
     <row r="15">
@@ -1362,17 +1362,17 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>67365959.5</v>
+        <v>72361.03999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4034-309-CM26</t>
+          <t>926853-51-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,52 +1392,48 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.160.501-9</t>
+          <t>65.120.506-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>Zona de Bienestar Valdivia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>99936200</v>
+        <v>32858.35</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>646-74-CM26</t>
+          <t>650-72-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1457,48 +1453,48 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.816.000-9</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.349.970-7</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>28498239</v>
+        <v>28862.8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5240-180-SE26</t>
+          <t>646-74-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1518,52 +1514,48 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>61.816.000-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION IV REGION</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SOCIEDAD HERMANAS CALLEGARI LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.349.970-7</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>112380000</v>
+        <v>30611.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>650-72-CM26</t>
+          <t>4034-309-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1583,48 +1575,52 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>69.160.501-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>Ilustre Municipalidad de Cañete - Educación</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26870399.92</v>
+        <v>107346.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>926853-51-CM26</t>
+          <t>5240-180-SE26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1649,37 +1645,41 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>65.120.506-9</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Valdivia</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>30590140</v>
+        <v>120712.8</v>
       </c>
     </row>
     <row r="21">
@@ -1736,17 +1736,17 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>20570199.58</v>
+        <v>22095.45</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>377-311-CM26</t>
+          <t>3801-36-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1761,53 +1761,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTO SUMMIT CHILE S.A.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.924.460-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>682740</v>
+        <v>48560.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3801-36-CM26</t>
+          <t>2483-461-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1832,43 +1832,43 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTO SUMMIT CHILE S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>96.924.460-8</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>45208100</v>
+        <v>15940.47</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2483-461-CM26</t>
+          <t>3820-637-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1888,48 +1888,48 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14840100.87</v>
+        <v>17244.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>3820-638-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1980,17 +1980,17 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>16054290</v>
+        <v>398.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>564953-704-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2010,48 +2010,48 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>70.902.000-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>371041</v>
+        <v>75591.86</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>564953-704-CM26</t>
+          <t>1195-408-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.902.000-5</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2102,11 +2102,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>70373753.52</v>
+        <v>73244.25</v>
       </c>
     </row>
     <row r="28">
@@ -2163,17 +2163,17 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>663480</v>
+        <v>712.6799999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1195-408-CM26</t>
+          <t>1596-185-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2224,17 +2224,17 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>68188199.52</v>
+        <v>41999.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>5240-169-CM26</t>
+          <t>2688-237-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2259,43 +2259,43 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>86.385.500-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>157350598.86</v>
+        <v>721.13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1743-372-CM26</t>
+          <t>2688-236-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2320,43 +2320,43 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>27796972</v>
+        <v>35561.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1743-373-CM26</t>
+          <t>1596-186-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2381,43 +2381,43 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>556212</v>
+        <v>1362.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1743-374-CM26</t>
+          <t>1077195-70-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2442,17 +2442,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>Administración de Fondos de Terceros</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2468,17 +2468,17 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>38529599.85</v>
+        <v>693.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1743-375-CM26</t>
+          <t>5240-169-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2503,43 +2503,43 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1042078</v>
+        <v>169017.9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1077195-69-CM26</t>
+          <t>1743-375-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2564,17 +2564,17 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2590,17 +2590,17 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>30650500.37</v>
+        <v>1119.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1077195-70-CM26</t>
+          <t>1743-374-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>82.983.100-7</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Administración de Fondos de Terceros</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2651,17 +2651,17 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>646080</v>
+        <v>41386.51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1596-185-CM26</t>
+          <t>1743-373-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2686,43 +2686,43 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>39100000.17</v>
+        <v>597.45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1596-186-CM26</t>
+          <t>1743-372-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2747,43 +2747,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1268052</v>
+        <v>29858.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2688-236-CM26</t>
+          <t>1077195-69-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>82.983.100-7</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>Administración de Fondos de Terceros</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2834,17 +2834,17 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>33106752</v>
+        <v>32923.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2688-237-CM26</t>
+          <t>1590-206-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2869,43 +2869,43 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.301.000-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>671352</v>
+        <v>22719.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1590-206-CM26</t>
+          <t>1422035-16-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.301.000-9</t>
+          <t>65.034.681-5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE AGRICULT</t>
+          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2945,28 +2945,28 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>21150800.58</v>
+        <v>32224.45</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1422035-16-CM26</t>
+          <t>1195104-212-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2981,53 +2981,53 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>65.034.681-5</t>
+          <t>62.000.920-2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CORPORACION REGIONAL DE DESARROLLO PRODUCTIVO DE LA REGION DEL MAULE</t>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>29999999.96</v>
+        <v>26853.71</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>4236-511-CM26</t>
+          <t>2885-339-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3052,43 +3052,43 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.160.200-1</t>
+          <t>69.210.600-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE PUYEHUE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>35625744</v>
+        <v>31943.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1195104-212-CM26</t>
+          <t>4236-511-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3108,48 +3108,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>69.160.200-1</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>25000000.76</v>
+        <v>38267.34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2885-339-CM26</t>
+          <t>4083-352-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3174,37 +3174,37 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.210.600-8</t>
+          <t>69.151.002-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUYEHUE</t>
+          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>29738100</v>
+        <v>37580.16</v>
       </c>
     </row>
     <row r="46">
@@ -3261,11 +3261,11 @@
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>29977290</v>
+        <v>32200.06</v>
       </c>
     </row>
     <row r="47">
@@ -3322,17 +3322,17 @@
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>30295499.57</v>
+        <v>32541.86</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>4083-352-CM26</t>
+          <t>1180885-32-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3357,43 +3357,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.151.002-6</t>
+          <t>61.606.300-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>SERVICIO DE SALUD ATACAMA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>34986000</v>
+        <v>34599.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2780-248-CM26</t>
+          <t>4494-544-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3418,43 +3418,43 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.150.500-6</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>31404100</v>
+        <v>34372.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1180885-32-CM26</t>
+          <t>2291-1276-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3479,43 +3479,43 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.606.300-6</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ATACAMA</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>32210999.73</v>
+        <v>32092.94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>4494-544-CM26</t>
+          <t>2780-248-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3540,43 +3540,43 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.150.500-6</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>79.853.470-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>31999999.64</v>
+        <v>33732.67</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2291-1276-CM26</t>
+          <t>2429-914-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3601,43 +3601,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>29877565.62</v>
+        <v>36686.67</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2963-81-CM26</t>
+          <t>1216088-218-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3662,12 +3662,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.072.400-6</t>
+          <t>65.065.121-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA GRANJA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3677,28 +3677,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>15999999.82</v>
+        <v>46897.23</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2429-914-CM26</t>
+          <t>1782-12-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Gobierno Regional de Antofagasta</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,28 +3738,32 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>34154190</v>
+        <v>650188.38</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1216088-218-CM26</t>
+          <t>2963-81-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3784,12 +3788,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>65.065.121-9</t>
+          <t>69.072.400-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES DE PUENTE ALTO</t>
+          <t>I MUNICIPALIDAD DE LA GRANJA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3799,28 +3803,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>43659910</v>
+        <v>17186.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1782-12-CM26</t>
+          <t>2429-915-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3845,12 +3849,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3860,87 +3864,22 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>605305876</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>2429-915-CM26</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2239-6-LR25</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>69.020.300-6</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>79.649.140-k</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="n">
-        <v>1371784</v>
+        <v>1473.5</v>
       </c>
     </row>
   </sheetData>
